--- a/Finalisation-concertation/ig/ValueSet-fr-editorial-status.xlsx
+++ b/Finalisation-concertation/ig/ValueSet-fr-editorial-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:36:59+00:00</t>
+    <t>2026-05-21T12:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
